--- a/docs/261016/ver2.5以降の起動オプション.xlsx
+++ b/docs/261016/ver2.5以降の起動オプション.xlsx
@@ -8,12 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gogow\Documents\ThinktankWebCC\docs\261016\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7364253A-F826-4099-8EBE-EB955B94EAC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA016FE1-4E13-4745-AD29-FA6C2CF85A8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{511C185D-BF54-4279-A048-E7F2BD1856B7}"/>
+    <workbookView xWindow="22932" yWindow="-72" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{511C185D-BF54-4279-A048-E7F2BD1856B7}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="起2動" sheetId="1" r:id="rId1"/>
+    <sheet name="起動" sheetId="4" r:id="rId2"/>
+    <sheet name="PM1" sheetId="2" r:id="rId3"/>
+    <sheet name="トリガーリスト(GTD)" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="162">
   <si>
     <t>アプリサーバー</t>
   </si>
@@ -48,9 +51,6 @@
     <t>開発時</t>
   </si>
   <si>
-    <t>製品版</t>
-  </si>
-  <si>
     <t>app://thinktank/index.html</t>
   </si>
   <si>
@@ -63,23 +63,11 @@
     <t>表示</t>
   </si>
   <si>
-    <t>npm run dev:vite</t>
-  </si>
-  <si>
     <t>npm run dev:web-relay</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>npm run relay:start</t>
-  </si>
-  <si>
     <t>PC のブラウザ</t>
-  </si>
-  <si>
-    <t>Firebase Hosting</t>
-  </si>
-  <si>
-    <t>https://thinktankweb-483408.web.app</t>
   </si>
   <si>
     <t>なし</t>
@@ -142,55 +130,68 @@
     <t>区分</t>
   </si>
   <si>
+    <t>Vault フォルダ（既定は G:）</t>
+  </si>
+  <si>
+    <t>ローカルの AI CLI</t>
+  </si>
+  <si>
+    <t>PC アプリ</t>
+  </si>
+  <si>
+    <t>①Firebase ②ローカル窓口</t>
+  </si>
+  <si>
+    <t>ローカル窓口（Drive API にも切替可）</t>
+  </si>
+  <si>
+    <t>一緒に起動される</t>
+  </si>
+  <si>
+    <t>なし（ログインページだけ）</t>
+  </si>
+  <si>
+    <t>これ自体</t>
+  </si>
+  <si>
+    <t>Web アプリ</t>
+  </si>
+  <si>
+    <t>携帯（または幅 768px 未満）</t>
+  </si>
+  <si>
+    <t>非表示</t>
+  </si>
+  <si>
+    <t>Vault フォルダ（既定は G:、なければ .staging_vault）</t>
+  </si>
+  <si>
+    <t>npm run electron:dev</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>npm run dev:vite</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>npm run relay:start</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ブラウザ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>FB への応答</t>
-  </si>
-  <si>
-    <t>Vault フォルダ（既定は G:）</t>
-  </si>
-  <si>
-    <t>ローカルの AI CLI</t>
-  </si>
-  <si>
-    <t>しない（ログインの入口なし）</t>
-  </si>
-  <si>
-    <t>PC アプリ</t>
-  </si>
-  <si>
-    <t>ブラウザ（自分で開く）</t>
-  </si>
-  <si>
-    <t>①Firebase ②ローカル窓口</t>
-  </si>
-  <si>
-    <t>ローカル窓口を選んだ場合は必要</t>
-  </si>
-  <si>
-    <t>ローカル窓口（Drive API にも切替可）</t>
-  </si>
-  <si>
-    <t>一緒に起動される</t>
-  </si>
-  <si>
-    <t>なし（ログインページだけ）</t>
-  </si>
-  <si>
-    <t>これ自体</t>
-  </si>
-  <si>
-    <t>Web アプリ</t>
-  </si>
-  <si>
-    <t>不要（予備として使うことあり）</t>
-  </si>
-  <si>
-    <t>携帯（または幅 768px 未満）</t>
-  </si>
-  <si>
-    <t>非表示</t>
-  </si>
-  <si>
-    <t>Vault フォルダ（既定は G:、なければ .staging_vault）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://thinktankweb-483408.web.app</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>* localhost:8080/relay-login</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <r>
@@ -199,7 +200,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="14"/>
+        <sz val="11"/>
         <color theme="1"/>
         <rFont val="Meiryo UI"/>
         <family val="3"/>
@@ -209,7 +210,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="14"/>
+        <sz val="11"/>
         <color theme="1"/>
         <rFont val="Meiryo UI"/>
         <family val="3"/>
@@ -219,15 +220,406 @@
     </r>
   </si>
   <si>
+    <t>不要
+（予備として使うことあり）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>開発時
+ローカル窓口</t>
+  </si>
+  <si>
+    <t>開発時
+ローカル窓口</t>
+    <rPh sb="0" eb="3">
+      <t>カイハツジ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>マドグチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>製品.exe</t>
+  </si>
+  <si>
+    <t>製品.exe</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>非表示/(Firebase)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>npm run dev:vite</t>
+  </si>
+  <si>
+    <t>npm run dev:web-relay</t>
+  </si>
+  <si>
+    <t>一緒に起動される</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ローカル窓口を選んだ場合は必要</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>分類（カテゴリ）</t>
+  </si>
+  <si>
+    <t>管理項目名</t>
+  </si>
+  <si>
+    <t>概要・管理する内容</t>
+  </si>
+  <si>
+    <t>1. 目的・成果管理（何を目指し、何を作るか）</t>
+  </si>
+  <si>
+    <t>プロジェクトの目的・達成指標（KPI）納品物やシステム、ドキュメント対象範囲と対象外の境界線検収条件やクリアすべき性能・仕様</t>
+  </si>
+  <si>
+    <t>2. 実行・工程管理（いつ、どのように進めるか）</t>
+  </si>
+  <si>
+    <t>最終納期および各フェーズの期日成果物を作るための具体的作業単位フェーズ移行や意思決定の重要節目各作業の消化率・遅延の有無</t>
+  </si>
+  <si>
+    <t>3. 資源・コスト管理（何を使って実現するか）</t>
+  </si>
+  <si>
+    <t>要員（人月・スキル）、設備、ライセンス人件費、外注費、経費などの資金枠外部ベンダー選定、購入契約、納品管理</t>
+  </si>
+  <si>
+    <t>4. 統制・不確実性管理（ブレや阻害要因にどう対処するか）</t>
+  </si>
+  <si>
+    <t>すでに発生している問題と解消計画将来起こりうる脅威の予防・影響緩和策仕様や要件変更の承認・影響度評価プロセス前提としている仮定や予算・期間の制限事項「なぜその判断を下したか」の合意履歴</t>
+  </si>
+  <si>
+    <t>5. 体制・連携管理（誰とどう協力するか）</t>
+  </si>
+  <si>
+    <t>顧客、社内関係者、最終ユーザーなどの利害関係者協業パートナー、委託先、関連官公庁など主担当・副担当・承認者の責任分界点定例会、エスカレーションルート、報告形式次回以降に活かす知見・トラブルの再発防止策</t>
+  </si>
+  <si>
+    <t>ゴール、成果物、スコープ、品質基準</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>締め切り、タスク、マイルストーン、進捗状況</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リソース、予算、調達・発注</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>課題、リスク、変更管理、前提・制約条件、意思決定ログ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステークホルダー、外部組織、役割と責任、コミュニケーション計画、ナレッジ・教訓</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>WHO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HOW</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>WHY、WHAT</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>WHERE</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>WHEN、HOW</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Thinktank</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Seeds</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Discuss</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Harvest</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>〇</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>npm run electron:dev</t>
-    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大項目</t>
+  </si>
+  <si>
+    <t>小項目</t>
+  </si>
+  <si>
+    <t>やりかけのプロジェクト</t>
+  </si>
+  <si>
+    <t>―</t>
+  </si>
+  <si>
+    <t>着手すべきプロジェクト</t>
+  </si>
+  <si>
+    <t>責任を負っていること、約束していること</t>
+  </si>
+  <si>
+    <t>上司・共同経営者／同僚／部下／他の従業員／社外（顧客、他社、専門家）</t>
+  </si>
+  <si>
+    <t>連絡</t>
+  </si>
+  <si>
+    <t>社内・社外／連絡または応答が必要な機器・ツール（電話、メール、FAX、手紙、メモ）</t>
+  </si>
+  <si>
+    <t>執筆・提出</t>
+  </si>
+  <si>
+    <t>報告書／評価・レビュー／提案／論考／販促／説明・指示／書き直し・編集</t>
+  </si>
+  <si>
+    <t>セッティングが必要な会議・面談</t>
+  </si>
+  <si>
+    <t>決定事項を知らせるべき相手</t>
+  </si>
+  <si>
+    <t>読むべき本や記事</t>
+  </si>
+  <si>
+    <t>財務</t>
+  </si>
+  <si>
+    <t>キャッシュフロー／各種データ／予算／予測・展望／損益／バランスシート／与信枠</t>
+  </si>
+  <si>
+    <t>プランニング・組織化</t>
+  </si>
+  <si>
+    <t>会社の戦略や目標／現行のプロジェクト／今後のプロジェクト／事業・マーケティングのプラン／予定されている行事／会議・面談／プレゼンテーション／組織／設備の変更／ITシステム・設備の導入／出張</t>
+  </si>
+  <si>
+    <t>銀行</t>
+  </si>
+  <si>
+    <t>受取勘定／支払勘定／小口現金</t>
+  </si>
+  <si>
+    <t>管理</t>
+  </si>
+  <si>
+    <t>法的問題／保険／人事／方針・手続き</t>
+  </si>
+  <si>
+    <t>顧客</t>
+  </si>
+  <si>
+    <t>社内／社外</t>
+  </si>
+  <si>
+    <t>マーケティング</t>
+  </si>
+  <si>
+    <t>販促</t>
+  </si>
+  <si>
+    <t>販売</t>
+  </si>
+  <si>
+    <t>カスタマーサービス</t>
+  </si>
+  <si>
+    <t>システム</t>
+  </si>
+  <si>
+    <t>電話／パソコン／オフィス設備／その他の設備／光熱・水道関係※／ファイリング※／保管・収納（在庫）※</t>
+  </si>
+  <si>
+    <t>備品</t>
+  </si>
+  <si>
+    <t>オフィス・職場</t>
+  </si>
+  <si>
+    <t>オフィスの空間／家具／装飾</t>
+  </si>
+  <si>
+    <t>連絡待ち事項</t>
+  </si>
+  <si>
+    <t>情報／他者に任せたタスク・プロジェクト／プロジェクトの要件／返信・応答…（手紙、メモ、電話、提案、要請、督促、小銭の貸し借り、保険、注文品、補修、チケット、他者による決定）</t>
+  </si>
+  <si>
+    <t>教育・研修</t>
+  </si>
+  <si>
+    <t>トレーニング・セミナー／習得事項／調査事項／習得・熟練の必要なスキル（パソコン）／ビデオを用いたトレーニング／履歴書</t>
+  </si>
+  <si>
+    <t>社外学習</t>
+  </si>
+  <si>
+    <t>リサーチが必要なこと</t>
+  </si>
+  <si>
+    <t>制服</t>
+  </si>
+  <si>
+    <t>夫・妻／子ども／家族／友人／専門家／借りている物</t>
+  </si>
+  <si>
+    <t>社外の組織に関するプロジェクト</t>
+  </si>
+  <si>
+    <t>サービス／市民活動／ボランティア</t>
+  </si>
+  <si>
+    <t>家族／友人／専門家／連絡または応答が必要な機器・ツール（電話、手紙・ハガキ、メッセージカード）</t>
+  </si>
+  <si>
+    <t>予定行事</t>
+  </si>
+  <si>
+    <t>特別行事／誕生日／記念日／結婚式／卒業式／休日／旅行／週末の予定／長期休暇／社会的行事／文化的行事／スポーツイベント</t>
+  </si>
+  <si>
+    <t>見聞を広げるために</t>
+  </si>
+  <si>
+    <t>行きたいところ／会いたい人、招きたい人／地元で体験してみたいこと</t>
+  </si>
+  <si>
+    <t>家計（請求書、銀行、投資、ローン、税金）／保険／法的問題／ファイリング</t>
+  </si>
+  <si>
+    <t>注文品／補修／督促／借り物／医療情報／出欠の返事</t>
+  </si>
+  <si>
+    <t>家関連</t>
+  </si>
+  <si>
+    <t>家主／土地所有（法律面、不動産、建築規制、税金、建築業者）／暖房・空調／水回り／電気／屋根／景観／敷地内舗装／壁・床・天井／内外装・装飾品／家具／備品／電化製品／電球・配線／台所用品／洗濯機・乾燥機・掃除機／整理や掃除が必要な場所／テレビ／ビデオ／音楽・CD／カメラ・フィルム／電話（留守電設定）／スポーツ用具／タンス・服／ガレージ・収納／車・自転車の補修・メンテ／工具／カバン類／ペット</t>
+  </si>
+  <si>
+    <t>パソコン</t>
+  </si>
+  <si>
+    <t>ソフト／ハード／接続／CD-ROM／メール・ネット</t>
+  </si>
+  <si>
+    <t>健康・医療</t>
+  </si>
+  <si>
+    <t>病院／専門治療</t>
+  </si>
+  <si>
+    <t>娯楽</t>
+  </si>
+  <si>
+    <t>本・レコード・テープ・CD</t>
+  </si>
+  <si>
+    <t>買い物・用事</t>
+  </si>
+  <si>
+    <t>ホームセンター／ドラッグストア／スーパー／銀行／クリーニング／文具店</t>
+  </si>
+  <si>
+    <t>地元</t>
+  </si>
+  <si>
+    <t>近所／学校／自治体</t>
+  </si>
+  <si>
+    <t>市民生活に関する問題</t>
+  </si>
+  <si>
+    <t>【プライベートについて】</t>
+  </si>
+  <si>
+    <t>【仕事について】</t>
+  </si>
+  <si>
+    <t>区分</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FB への応答</t>
+  </si>
+  <si>
+    <t>正本：Firestore
+バックアップ：Vault フォルダ（G:、なければ userData）</t>
+  </si>
+  <si>
+    <t>ローカルの AI CLI（IPC で直接）</t>
+  </si>
+  <si>
+    <t>応答する*</t>
+  </si>
+  <si>
+    <t>ブラウザ</t>
+  </si>
+  <si>
+    <t>Firestore のみ</t>
+  </si>
+  <si>
+    <t>①Firebase 中継（リアルタイム）
+②中継役がオフラインなら localhost:8080 に直接送る</t>
+  </si>
+  <si>
+    <t>不要（あれば②で使う）</t>
+  </si>
+  <si>
+    <t>npm run relay:start</t>
+  </si>
+  <si>
+    <t>Think は扱わない
+（Vault フォルダ：G:、なければ .staging_vault）</t>
+  </si>
+  <si>
+    <t>https://thinktankweb-483408.web.app</t>
+  </si>
+  <si>
+    <t>Firestore のみ
+（保存・本文・一覧・検索すべて）</t>
+  </si>
+  <si>
+    <t>Firebase 中継（リアルタイム）→ 中継役 PC の AI CLI</t>
+  </si>
+  <si>
+    <t>携帯（または幅 767px 以下）</t>
+  </si>
+  <si>
+    <t>* Firebase へのログインが必要（relay:start / dev:web-relay は http://localhost:8080/relay-login でログイン）</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -251,7 +643,39 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="12"/>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Meiryo UI"/>
       <family val="3"/>
@@ -259,22 +683,62 @@
     </font>
     <font>
       <b/>
-      <sz val="14"/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF0563C1"/>
       <name val="Meiryo UI"/>
       <family val="3"/>
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E1F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -297,43 +761,117 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="標準 2" xfId="2" xr:uid="{8C2F095F-77C0-4B4C-8125-3444AD05CB3B}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -645,261 +1183,1049 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6DDD599-07F0-41D9-A4D9-14A448D27FD3}">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A2:I10"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="4.125" style="8" customWidth="1"/>
-    <col min="2" max="2" width="13.25" style="8" customWidth="1"/>
-    <col min="3" max="3" width="31.375" style="5" customWidth="1"/>
-    <col min="4" max="4" width="24.25" style="8" customWidth="1"/>
-    <col min="5" max="5" width="42.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="48.125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="28.625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20.5" style="8" customWidth="1"/>
-    <col min="9" max="9" width="32.875" style="8" customWidth="1"/>
+    <col min="1" max="1" width="4.125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="13.25" style="3" customWidth="1"/>
+    <col min="3" max="3" width="31.375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="14.25" style="3" customWidth="1"/>
+    <col min="5" max="5" width="29.25" style="1" customWidth="1"/>
+    <col min="6" max="6" width="37" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="19.75" style="3" customWidth="1"/>
+    <col min="9" max="9" width="12.75" style="3" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="39" x14ac:dyDescent="0.4">
-      <c r="A1" s="6" t="s">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A3" s="5">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A4" s="12">
+        <v>2</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="31.5" x14ac:dyDescent="0.4">
+      <c r="A5" s="5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="H5" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="31.5" x14ac:dyDescent="0.4">
+      <c r="A6" s="5">
+        <v>4</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="6" t="s">
+      <c r="G6" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="31.5" x14ac:dyDescent="0.4">
+      <c r="A7" s="5">
+        <v>5</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="63" x14ac:dyDescent="0.4">
+      <c r="A8" s="12">
+        <v>6</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="31.5" x14ac:dyDescent="0.4">
+      <c r="A9" s="12">
+        <v>7</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A10" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="9"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="B8" r:id="rId1" display="https://thinktankweb-483408.web.app" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="D8" r:id="rId2" display="https://thinktankweb-483408.web.app" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="B9" r:id="rId3" display="https://thinktankweb-483408.web.app" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="D9" r:id="rId4" display="https://thinktankweb-483408.web.app" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="C8:C9" r:id="rId5" display="https://thinktankweb-483408.web.app" xr:uid="{5281D5B2-A938-4E10-8D95-8A171B235589}"/>
+    <hyperlink ref="E9" r:id="rId6" xr:uid="{7242E09A-2DF1-48C2-B281-8339D7C6C237}"/>
+    <hyperlink ref="E8" r:id="rId7" xr:uid="{3888A3EB-1904-4584-8C97-680FC9EB113B}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId8"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F821A416-B5A6-4152-84DC-B49B186F5C3A}">
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="10.5" customWidth="1"/>
+    <col min="2" max="2" width="22.375" customWidth="1"/>
+    <col min="3" max="3" width="17.5" customWidth="1"/>
+    <col min="4" max="4" width="38" customWidth="1"/>
+    <col min="5" max="5" width="29.375" customWidth="1"/>
+    <col min="6" max="6" width="30.75" customWidth="1"/>
+    <col min="7" max="7" width="22.375" customWidth="1"/>
+    <col min="8" max="8" width="12.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A1" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="E1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="F1" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="G1" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="23" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="42.75" x14ac:dyDescent="0.4">
+      <c r="A2" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="E2" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="G2" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="24" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="42.75" x14ac:dyDescent="0.4">
+      <c r="A3" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="G3" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="24" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="42.75" x14ac:dyDescent="0.4">
+      <c r="A4" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="F4" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="G4" s="24" t="s">
+        <v>154</v>
+      </c>
+      <c r="H4" s="24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="42.75" x14ac:dyDescent="0.4">
+      <c r="A5" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="F5" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="G5" s="24" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A2" s="4">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="H5" s="24" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="42.75" x14ac:dyDescent="0.4">
+      <c r="A6" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>155</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="F6" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="24" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="42.75" x14ac:dyDescent="0.4">
+      <c r="A7" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>158</v>
+      </c>
+      <c r="F7" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="G7" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2" s="4" t="s">
+      <c r="H7" s="24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="42.75" x14ac:dyDescent="0.4">
+      <c r="A8" s="24" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A3" s="4">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="B8" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>160</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>158</v>
+      </c>
+      <c r="F8" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="39" x14ac:dyDescent="0.4">
-      <c r="A4" s="4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A5" s="4">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="39" x14ac:dyDescent="0.4">
-      <c r="A6" s="4">
-        <v>5</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="78" x14ac:dyDescent="0.4">
-      <c r="A7" s="4">
-        <v>6</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="7" t="s">
+      <c r="H8" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="4">
-        <v>7</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A9" s="5" t="s">
-        <v>23</v>
-      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A9" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="B9" s="22"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="B7" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="D7" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="B8" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="D8" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5385B15A-1E82-4AA8-852C-5082ACA6D30B}">
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="45" style="14" customWidth="1"/>
+    <col min="2" max="2" width="13.875" style="9" customWidth="1"/>
+    <col min="3" max="3" width="32.75" style="14" customWidth="1"/>
+    <col min="4" max="4" width="56.625" style="14" customWidth="1"/>
+    <col min="5" max="8" width="9" style="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="28.5" x14ac:dyDescent="0.4">
+      <c r="A2" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="H2" s="16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="28.5" x14ac:dyDescent="0.4">
+      <c r="A3" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="H3" s="17"/>
+    </row>
+    <row r="4" spans="1:8" ht="28.5" x14ac:dyDescent="0.4">
+      <c r="A4" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" s="17"/>
+      <c r="F4" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="42.75" x14ac:dyDescent="0.4">
+      <c r="A5" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="E5" s="17"/>
+      <c r="F5" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="H5" s="17"/>
+    </row>
+    <row r="6" spans="1:8" ht="42.75" x14ac:dyDescent="0.4">
+      <c r="A6" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" s="17"/>
+      <c r="F6" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="H6" s="17"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36EF56C0-076B-4893-97B9-E5F19403423E}">
+  <dimension ref="A1:B46"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="50.875" customWidth="1"/>
+    <col min="2" max="2" width="121.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A2" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A3" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A4" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A5" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A7" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A8" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A9" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A10" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A11" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A12" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A13" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A14" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A15" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A16" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A17" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A18" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A19" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A20" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A21" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A22" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A23" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A24" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A25" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A26" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A29" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A30" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="B30" s="21" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A31" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A32" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A33" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A34" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A35" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A36" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A37" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A38" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A39" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="75" x14ac:dyDescent="0.4">
+      <c r="A40" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="B40" s="13" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A41" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="B41" s="13" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A42" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="B42" s="13" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A43" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="B43" s="13" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A44" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="B44" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A45" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="B45" s="13" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A46" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/docs/261016/ver2.5以降の起動オプション.xlsx
+++ b/docs/261016/ver2.5以降の起動オプション.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gogow\Documents\ThinktankWebCC\docs\261016\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA016FE1-4E13-4745-AD29-FA6C2CF85A8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A068447C-65BB-45A9-9934-0F8E051FA115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-72" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{511C185D-BF54-4279-A048-E7F2BD1856B7}"/>
+    <workbookView xWindow="22932" yWindow="-72" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{511C185D-BF54-4279-A048-E7F2BD1856B7}"/>
   </bookViews>
   <sheets>
-    <sheet name="起2動" sheetId="1" r:id="rId1"/>
-    <sheet name="起動" sheetId="4" r:id="rId2"/>
-    <sheet name="PM1" sheetId="2" r:id="rId3"/>
-    <sheet name="トリガーリスト(GTD)" sheetId="3" r:id="rId4"/>
+    <sheet name="起動" sheetId="4" r:id="rId1"/>
+    <sheet name="PM1" sheetId="2" r:id="rId2"/>
+    <sheet name="トリガーリスト(GTD)" sheetId="3" r:id="rId3"/>
+    <sheet name="起2動" sheetId="1" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="159">
   <si>
     <t>アプリサーバー</t>
   </si>
@@ -143,9 +143,6 @@
   </si>
   <si>
     <t>ローカル窓口（Drive API にも切替可）</t>
-  </si>
-  <si>
-    <t>一緒に起動される</t>
   </si>
   <si>
     <t>なし（ログインページだけ）</t>
@@ -227,10 +224,6 @@
   <si>
     <t>開発時
 ローカル窓口</t>
-  </si>
-  <si>
-    <t>開発時
-ローカル窓口</t>
     <rPh sb="0" eb="3">
       <t>カイハツジ</t>
     </rPh>
@@ -254,9 +247,6 @@
     <t>npm run dev:vite</t>
   </si>
   <si>
-    <t>npm run dev:web-relay</t>
-  </si>
-  <si>
     <t>一緒に起動される</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -592,13 +582,6 @@
     <t>不要（あれば②で使う）</t>
   </si>
   <si>
-    <t>npm run relay:start</t>
-  </si>
-  <si>
-    <t>Think は扱わない
-（Vault フォルダ：G:、なければ .staging_vault）</t>
-  </si>
-  <si>
     <t>https://thinktankweb-483408.web.app</t>
   </si>
   <si>
@@ -613,6 +596,23 @@
   </si>
   <si>
     <t>* Firebase へのログインが必要（relay:start / dev:web-relay は http://localhost:8080/relay-login でログイン）</t>
+  </si>
+  <si>
+    <t>次にすること</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>締め切り</t>
+    <rPh sb="0" eb="1">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -786,7 +786,7 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -835,7 +835,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -843,9 +843,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1182,6 +1179,734 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F821A416-B5A6-4152-84DC-B49B186F5C3A}">
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="10.5" customWidth="1"/>
+    <col min="2" max="2" width="22.375" customWidth="1"/>
+    <col min="3" max="3" width="17.5" customWidth="1"/>
+    <col min="4" max="4" width="38" customWidth="1"/>
+    <col min="5" max="5" width="29.375" customWidth="1"/>
+    <col min="6" max="6" width="30.75" customWidth="1"/>
+    <col min="7" max="7" width="22.375" customWidth="1"/>
+    <col min="8" max="8" width="12.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A1" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="22" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="42.75" x14ac:dyDescent="0.4">
+      <c r="A2" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="F2" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="G2" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="23" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="42.75" x14ac:dyDescent="0.4">
+      <c r="A3" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="F3" s="24" t="s">
+        <v>150</v>
+      </c>
+      <c r="G3" s="23" t="s">
+        <v>151</v>
+      </c>
+      <c r="H3" s="23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="42.75" x14ac:dyDescent="0.4">
+      <c r="A4" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="F4" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="G4" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4" s="23" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="28.5" x14ac:dyDescent="0.4">
+      <c r="A5" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>153</v>
+      </c>
+      <c r="F5" s="24" t="s">
+        <v>154</v>
+      </c>
+      <c r="G5" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="H5" s="23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="28.5" x14ac:dyDescent="0.4">
+      <c r="A6" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>155</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>153</v>
+      </c>
+      <c r="F6" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="H6" s="23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A7" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="B7" s="21"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="B5" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="D5" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="B6" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="D6" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5385B15A-1E82-4AA8-852C-5082ACA6D30B}">
+  <dimension ref="B1:I10"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="4.75" customWidth="1"/>
+    <col min="2" max="2" width="45" style="14" customWidth="1"/>
+    <col min="3" max="3" width="13.875" style="9" customWidth="1"/>
+    <col min="4" max="4" width="32.75" style="14" customWidth="1"/>
+    <col min="5" max="5" width="56.625" style="14" customWidth="1"/>
+    <col min="6" max="9" width="9" style="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:9" s="15" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="B1" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" s="7"/>
+      <c r="D1" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="2:9" ht="28.5" x14ac:dyDescent="0.4">
+      <c r="B2" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="H2" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="I2" s="16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" ht="28.5" x14ac:dyDescent="0.4">
+      <c r="B3" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="H3" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="I3" s="17"/>
+    </row>
+    <row r="4" spans="2:9" ht="28.5" x14ac:dyDescent="0.4">
+      <c r="B4" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" s="17"/>
+      <c r="G4" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="I4" s="16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" ht="42.75" x14ac:dyDescent="0.4">
+      <c r="B5" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F5" s="17"/>
+      <c r="G5" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="I5" s="17"/>
+    </row>
+    <row r="6" spans="2:9" ht="42.75" x14ac:dyDescent="0.4">
+      <c r="B6" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="F6" s="17"/>
+      <c r="G6" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="H6" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="I6" s="17"/>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B9" s="14" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B10" s="14" t="s">
+        <v>158</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36EF56C0-076B-4893-97B9-E5F19403423E}">
+  <dimension ref="A1:B46"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="50.875" customWidth="1"/>
+    <col min="2" max="2" width="121.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A2" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A3" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A4" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A5" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A7" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A8" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A9" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A10" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A11" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A12" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A13" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A14" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A15" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A16" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A17" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A18" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A19" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A20" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A21" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A22" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A23" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A24" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A25" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A26" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A29" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A30" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="B30" s="20" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A31" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A32" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A33" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A34" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A35" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A36" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A37" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A38" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A39" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="75" x14ac:dyDescent="0.4">
+      <c r="A40" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="B40" s="13" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A41" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="B41" s="13" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A42" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="B42" s="13" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A43" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="B43" s="13" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A44" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="B44" s="13" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A45" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="B45" s="13" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A46" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>81</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6DDD599-07F0-41D9-A4D9-14A448D27FD3}">
   <dimension ref="A2:I10"/>
   <sheetFormatPr defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
@@ -1203,7 +1928,7 @@
         <v>20</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>15</v>
@@ -1224,7 +1949,7 @@
         <v>11</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.4">
@@ -1235,7 +1960,7 @@
         <v>3</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>5</v>
@@ -1264,7 +1989,7 @@
         <v>24</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>5</v>
@@ -1293,22 +2018,22 @@
         <v>3</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>25</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="I5" s="5" t="s">
         <v>14</v>
@@ -1325,7 +2050,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>16</v>
@@ -1337,7 +2062,7 @@
         <v>25</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>17</v>
@@ -1348,25 +2073,25 @@
         <v>5</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>23</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I7" s="7" t="s">
         <v>17</v>
@@ -1377,25 +2102,25 @@
         <v>6</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="19" t="s">
         <v>19</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>13</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I8" s="5" t="s">
         <v>14</v>
@@ -1406,22 +2131,22 @@
         <v>7</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>31</v>
-      </c>
       <c r="E9" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>12</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>6</v>
@@ -1437,7 +2162,7 @@
       <c r="B10" s="9"/>
       <c r="C10" s="8"/>
       <c r="D10" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E10" s="10"/>
       <c r="F10" s="10"/>
@@ -1459,773 +2184,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId8"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F821A416-B5A6-4152-84DC-B49B186F5C3A}">
-  <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="10.5" customWidth="1"/>
-    <col min="2" max="2" width="22.375" customWidth="1"/>
-    <col min="3" max="3" width="17.5" customWidth="1"/>
-    <col min="4" max="4" width="38" customWidth="1"/>
-    <col min="5" max="5" width="29.375" customWidth="1"/>
-    <col min="6" max="6" width="30.75" customWidth="1"/>
-    <col min="7" max="7" width="22.375" customWidth="1"/>
-    <col min="8" max="8" width="12.375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A1" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="H1" s="23" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="42.75" x14ac:dyDescent="0.4">
-      <c r="A2" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="C2" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="25" t="s">
-        <v>148</v>
-      </c>
-      <c r="F2" s="25" t="s">
-        <v>149</v>
-      </c>
-      <c r="G2" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" s="24" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="42.75" x14ac:dyDescent="0.4">
-      <c r="A3" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="C3" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="25" t="s">
-        <v>148</v>
-      </c>
-      <c r="F3" s="25" t="s">
-        <v>149</v>
-      </c>
-      <c r="G3" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" s="24" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="42.75" x14ac:dyDescent="0.4">
-      <c r="A4" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" s="24" t="s">
-        <v>151</v>
-      </c>
-      <c r="D4" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="F4" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="G4" s="24" t="s">
-        <v>154</v>
-      </c>
-      <c r="H4" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="42.75" x14ac:dyDescent="0.4">
-      <c r="A5" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="25" t="s">
-        <v>49</v>
-      </c>
-      <c r="C5" s="24" t="s">
-        <v>151</v>
-      </c>
-      <c r="D5" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="F5" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="G5" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5" s="24" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="42.75" x14ac:dyDescent="0.4">
-      <c r="A6" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="B6" s="25" t="s">
-        <v>155</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="25" t="s">
-        <v>156</v>
-      </c>
-      <c r="F6" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6" s="24" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="42.75" x14ac:dyDescent="0.4">
-      <c r="A7" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="26" t="s">
-        <v>157</v>
-      </c>
-      <c r="C7" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="26" t="s">
-        <v>157</v>
-      </c>
-      <c r="E7" s="25" t="s">
-        <v>158</v>
-      </c>
-      <c r="F7" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="G7" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="H7" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="42.75" x14ac:dyDescent="0.4">
-      <c r="A8" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>157</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>160</v>
-      </c>
-      <c r="D8" s="26" t="s">
-        <v>157</v>
-      </c>
-      <c r="E8" s="25" t="s">
-        <v>158</v>
-      </c>
-      <c r="F8" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="G8" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="H8" s="24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A9" s="27" t="s">
-        <v>161</v>
-      </c>
-      <c r="B9" s="22"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="22"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <hyperlinks>
-    <hyperlink ref="B7" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="D7" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="B8" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="D8" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5385B15A-1E82-4AA8-852C-5082ACA6D30B}">
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="45" style="14" customWidth="1"/>
-    <col min="2" max="2" width="13.875" style="9" customWidth="1"/>
-    <col min="3" max="3" width="32.75" style="14" customWidth="1"/>
-    <col min="4" max="4" width="56.625" style="14" customWidth="1"/>
-    <col min="5" max="8" width="9" style="15"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="D1" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="E1" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="F1" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="G1" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="H1" s="16" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="28.5" x14ac:dyDescent="0.4">
-      <c r="A2" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="D2" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="E2" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="F2" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="G2" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="H2" s="16" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="28.5" x14ac:dyDescent="0.4">
-      <c r="A3" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="E3" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="G3" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="H3" s="17"/>
-    </row>
-    <row r="4" spans="1:8" ht="28.5" x14ac:dyDescent="0.4">
-      <c r="A4" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" s="17"/>
-      <c r="F4" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="G4" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="H4" s="16" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="42.75" x14ac:dyDescent="0.4">
-      <c r="A5" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="E5" s="17"/>
-      <c r="F5" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="G5" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="H5" s="17"/>
-    </row>
-    <row r="6" spans="1:8" ht="42.75" x14ac:dyDescent="0.4">
-      <c r="A6" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="E6" s="17"/>
-      <c r="F6" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="G6" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="H6" s="17"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36EF56C0-076B-4893-97B9-E5F19403423E}">
-  <dimension ref="A1:B46"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="50.875" customWidth="1"/>
-    <col min="2" max="2" width="121.625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A2" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="B2" s="21" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A3" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A4" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A5" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A6" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A7" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A8" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A9" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A10" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A11" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A12" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A13" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A14" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A15" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A16" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A17" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A18" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A19" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A20" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A21" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A22" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A23" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A24" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="B24" s="13" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A25" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A26" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="B26" s="13" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A29" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A30" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="B30" s="21" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A31" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="B31" s="13" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A32" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="B32" s="13" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A33" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="B33" s="13" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A34" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="B34" s="13" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A35" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="B35" s="13" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A36" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="B36" s="13" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A37" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="B37" s="13" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A38" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="B38" s="13" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A39" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="B39" s="13" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" ht="75" x14ac:dyDescent="0.4">
-      <c r="A40" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="B40" s="13" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A41" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="B41" s="13" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A42" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="B42" s="13" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A43" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="B43" s="13" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A44" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="B44" s="13" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A45" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="B45" s="13" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A46" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="B46" s="13" t="s">
-        <v>84</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>